--- a/artfynd/A 5812-2025 artfynd.xlsx
+++ b/artfynd/A 5812-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123283263</v>
+        <v>123284673</v>
       </c>
       <c r="B2" t="n">
-        <v>5193</v>
+        <v>56691</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fisklösen, Fisklösen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528875</v>
+        <v>529284</v>
       </c>
       <c r="R2" t="n">
-        <v>6715153</v>
+        <v>6715159</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123284001</v>
+        <v>123286828</v>
       </c>
       <c r="B3" t="n">
-        <v>97319</v>
+        <v>98368</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529120</v>
+        <v>529029</v>
       </c>
       <c r="R3" t="n">
-        <v>6715242</v>
+        <v>6715126</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,12 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:38</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Fin naturlig bäck med utvidgning.</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123284673</v>
+        <v>123283263</v>
       </c>
       <c r="B4" t="n">
-        <v>56688</v>
+        <v>5193</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,42 +920,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fisklösen, Fisklösen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529284</v>
+        <v>528875</v>
       </c>
       <c r="R4" t="n">
-        <v>6715159</v>
+        <v>6715153</v>
       </c>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,22 +1004,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123283866</v>
+        <v>123303107</v>
       </c>
       <c r="B5" t="n">
-        <v>8441</v>
+        <v>98368</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,41 +1028,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fisklösen, Fisklösen, Dlr</t>
+          <t>Fisklösen, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528909</v>
+        <v>529050</v>
       </c>
       <c r="R5" t="n">
-        <v>6715166</v>
+        <v>6715233</v>
       </c>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1105,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt med bladrosetter på mindre yta.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,28 +1119,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123286828</v>
+        <v>123284001</v>
       </c>
       <c r="B6" t="n">
-        <v>98365</v>
+        <v>97322</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,25 +1150,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,13 +1178,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529029</v>
+        <v>529120</v>
       </c>
       <c r="R6" t="n">
-        <v>6715126</v>
+        <v>6715242</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1223,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Fin naturlig bäck med utvidgning.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123286624</v>
+        <v>123283866</v>
       </c>
       <c r="B7" t="n">
-        <v>56688</v>
+        <v>8441</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,42 +1271,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fisklösen, Fisklösen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529086</v>
+        <v>528909</v>
       </c>
       <c r="R7" t="n">
-        <v>6715119</v>
+        <v>6715166</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1325,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,22 +1355,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123303107</v>
+        <v>123283225</v>
       </c>
       <c r="B8" t="n">
-        <v>98365</v>
+        <v>92236</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,45 +1379,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fisklösen, Falun, Dlr</t>
+          <t>Fisklösen, Fisklösen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529050</v>
+        <v>528881</v>
       </c>
       <c r="R8" t="n">
-        <v>6715233</v>
+        <v>6715154</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1441,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,12 +1461,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt med bladrosetter på mindre yta.</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,7 +1470,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1484,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123286775</v>
+        <v>123286624</v>
       </c>
       <c r="B9" t="n">
-        <v>98365</v>
+        <v>56691</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,38 +1500,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fisklösen, Fisklösen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529026</v>
+        <v>529086</v>
       </c>
       <c r="R9" t="n">
-        <v>6715120</v>
+        <v>6715119</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,12 +1578,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt på cirka 3x0,5 meter</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,10 +1605,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123283225</v>
+        <v>123286775</v>
       </c>
       <c r="B10" t="n">
-        <v>92233</v>
+        <v>98368</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1613,47 +1617,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fisklösen, Fisklösen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528881</v>
+        <v>529026</v>
       </c>
       <c r="R10" t="n">
-        <v>6715154</v>
+        <v>6715120</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1685,7 +1680,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1695,7 +1690,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt på cirka 3x0,5 meter</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 5812-2025 artfynd.xlsx
+++ b/artfynd/A 5812-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123284673</v>
+        <v>123284001</v>
       </c>
       <c r="B2" t="n">
-        <v>56691</v>
+        <v>97324</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fisklösen, Fisklösen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529284</v>
+        <v>529120</v>
       </c>
       <c r="R2" t="n">
-        <v>6715159</v>
+        <v>6715242</v>
       </c>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Fin naturlig bäck med utvidgning.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,12 +780,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -795,7 +795,7 @@
         <v>123286828</v>
       </c>
       <c r="B3" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123283263</v>
+        <v>123286775</v>
       </c>
       <c r="B4" t="n">
-        <v>5193</v>
+        <v>98370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,25 +916,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,13 +944,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528875</v>
+        <v>529026</v>
       </c>
       <c r="R4" t="n">
-        <v>6715153</v>
+        <v>6715120</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt på cirka 3x0,5 meter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123303107</v>
+        <v>123283263</v>
       </c>
       <c r="B5" t="n">
-        <v>98368</v>
+        <v>5193</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,45 +1033,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fisklösen, Falun, Dlr</t>
+          <t>Fisklösen, Fisklösen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529050</v>
+        <v>528875</v>
       </c>
       <c r="R5" t="n">
-        <v>6715233</v>
+        <v>6715153</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,12 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt med bladrosetter på mindre yta.</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,7 +1115,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1138,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123284001</v>
+        <v>123283225</v>
       </c>
       <c r="B6" t="n">
-        <v>97322</v>
+        <v>92238</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,34 +1149,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fisklösen, Fisklösen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529120</v>
+        <v>528881</v>
       </c>
       <c r="R6" t="n">
-        <v>6715242</v>
+        <v>6715154</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,12 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:38</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Fin naturlig bäck med utvidgning.</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123283866</v>
+        <v>123284673</v>
       </c>
       <c r="B7" t="n">
-        <v>8441</v>
+        <v>56691</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,34 +1270,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fisklösen, Fisklösen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528909</v>
+        <v>529284</v>
       </c>
       <c r="R7" t="n">
-        <v>6715166</v>
+        <v>6715159</v>
       </c>
       <c r="S7" t="n">
         <v>13</v>
@@ -1330,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123283225</v>
+        <v>123303107</v>
       </c>
       <c r="B8" t="n">
-        <v>92236</v>
+        <v>98370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,50 +1383,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fisklösen, Fisklösen, Dlr</t>
+          <t>Fisklösen, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528881</v>
+        <v>529050</v>
       </c>
       <c r="R8" t="n">
-        <v>6715154</v>
+        <v>6715233</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1451,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,7 +1460,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt med bladrosetter på mindre yta.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,6 +1474,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1481,17 +1486,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson, Göran Ehn, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123286624</v>
+        <v>123283866</v>
       </c>
       <c r="B9" t="n">
-        <v>56691</v>
+        <v>8441</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,42 +1509,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fisklösen, Fisklösen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529086</v>
+        <v>528909</v>
       </c>
       <c r="R9" t="n">
-        <v>6715119</v>
+        <v>6715166</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1593,22 +1593,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123286775</v>
+        <v>123286624</v>
       </c>
       <c r="B10" t="n">
-        <v>98368</v>
+        <v>56691</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,38 +1617,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fisklösen, Fisklösen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529026</v>
+        <v>529086</v>
       </c>
       <c r="R10" t="n">
-        <v>6715120</v>
+        <v>6715119</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1690,12 +1695,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt på cirka 3x0,5 meter</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 5812-2025 artfynd.xlsx
+++ b/artfynd/A 5812-2025 artfynd.xlsx
@@ -1254,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123284673</v>
+        <v>123303107</v>
       </c>
       <c r="B7" t="n">
-        <v>56691</v>
+        <v>98370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,46 +1266,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fisklösen, Fisklösen, Dlr</t>
+          <t>Fisklösen, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529284</v>
+        <v>529050</v>
       </c>
       <c r="R7" t="n">
-        <v>6715159</v>
+        <v>6715233</v>
       </c>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1334,7 +1333,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1343,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt med bladrosetter på mindre yta.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,28 +1357,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Lisa Olson, Göran Ehn, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123303107</v>
+        <v>123284673</v>
       </c>
       <c r="B8" t="n">
-        <v>98370</v>
+        <v>56691</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,45 +1388,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fisklösen, Falun, Dlr</t>
+          <t>Fisklösen, Fisklösen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529050</v>
+        <v>529284</v>
       </c>
       <c r="R8" t="n">
-        <v>6715233</v>
+        <v>6715159</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1450,7 +1456,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,12 +1466,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt med bladrosetter på mindre yta.</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,19 +1475,18 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lisa Olson, Göran Ehn, Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 5812-2025 artfynd.xlsx
+++ b/artfynd/A 5812-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123284001</v>
+        <v>123283866</v>
       </c>
       <c r="B2" t="n">
-        <v>97324</v>
+        <v>8441</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529120</v>
+        <v>528909</v>
       </c>
       <c r="R2" t="n">
-        <v>6715242</v>
+        <v>6715166</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:38</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Fin naturlig bäck med utvidgning.</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123286828</v>
+        <v>123303107</v>
       </c>
       <c r="B3" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,19 +821,23 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fisklösen, Fisklösen, Dlr</t>
+          <t>Fisklösen, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529029</v>
+        <v>529050</v>
       </c>
       <c r="R3" t="n">
-        <v>6715126</v>
+        <v>6715233</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +876,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt med bladrosetter på mindre yta.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,6 +890,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -904,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123286775</v>
+        <v>123286828</v>
       </c>
       <c r="B4" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -944,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529026</v>
+        <v>529029</v>
       </c>
       <c r="R4" t="n">
-        <v>6715120</v>
+        <v>6715126</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:04</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt på cirka 3x0,5 meter</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123283263</v>
+        <v>123286624</v>
       </c>
       <c r="B5" t="n">
-        <v>5193</v>
+        <v>56691</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,37 +1037,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fisklösen, Fisklösen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528875</v>
+        <v>529086</v>
       </c>
       <c r="R5" t="n">
-        <v>6715153</v>
+        <v>6715119</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123283225</v>
+        <v>123283263</v>
       </c>
       <c r="B6" t="n">
-        <v>92238</v>
+        <v>5193</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,46 +1154,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fisklösen, Fisklösen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528881</v>
+        <v>528875</v>
       </c>
       <c r="R6" t="n">
-        <v>6715154</v>
+        <v>6715153</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1217,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123303107</v>
+        <v>123284001</v>
       </c>
       <c r="B7" t="n">
-        <v>98370</v>
+        <v>97330</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,45 +1262,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fisklösen, Falun, Dlr</t>
+          <t>Fisklösen, Fisklösen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529050</v>
+        <v>529120</v>
       </c>
       <c r="R7" t="n">
-        <v>6715233</v>
+        <v>6715242</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1333,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1343,12 +1335,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt med bladrosetter på mindre yta.</t>
+          <t>Fin naturlig bäck med utvidgning.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,7 +1349,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1369,17 +1360,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lisa Olson, Göran Ehn, Cecilia Rastad</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123284673</v>
+        <v>123286775</v>
       </c>
       <c r="B8" t="n">
-        <v>56691</v>
+        <v>98376</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,46 +1379,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fisklösen, Fisklösen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529284</v>
+        <v>529026</v>
       </c>
       <c r="R8" t="n">
-        <v>6715159</v>
+        <v>6715120</v>
       </c>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1456,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,7 +1452,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt på cirka 3x0,5 meter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,22 +1472,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123283866</v>
+        <v>123283225</v>
       </c>
       <c r="B9" t="n">
-        <v>8441</v>
+        <v>92244</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1509,37 +1500,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fisklösen, Fisklösen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528909</v>
+        <v>528881</v>
       </c>
       <c r="R9" t="n">
-        <v>6715166</v>
+        <v>6715154</v>
       </c>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1593,19 +1593,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123286624</v>
+        <v>123284673</v>
       </c>
       <c r="B10" t="n">
         <v>56691</v>
@@ -1641,7 +1641,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1650,13 +1650,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529086</v>
+        <v>529284</v>
       </c>
       <c r="R10" t="n">
-        <v>6715119</v>
+        <v>6715159</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,12 +1710,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 5812-2025 artfynd.xlsx
+++ b/artfynd/A 5812-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123284673</v>
       </c>
       <c r="B2" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123283263</v>
+        <v>123284001</v>
       </c>
       <c r="B3" t="n">
-        <v>5193</v>
+        <v>97350</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528875</v>
+        <v>529120</v>
       </c>
       <c r="R3" t="n">
-        <v>6715153</v>
+        <v>6715242</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Fin naturlig bäck med utvidgning.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123283866</v>
+        <v>123303107</v>
       </c>
       <c r="B4" t="n">
-        <v>8441</v>
+        <v>98396</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,41 +921,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fisklösen, Fisklösen, Dlr</t>
+          <t>Fisklösen, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528909</v>
+        <v>529050</v>
       </c>
       <c r="R4" t="n">
-        <v>6715166</v>
+        <v>6715233</v>
       </c>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +998,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt med bladrosetter på mindre yta.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,18 +1012,19 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1019,7 +1034,7 @@
         <v>123286775</v>
       </c>
       <c r="B5" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1133,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123284001</v>
+        <v>123283263</v>
       </c>
       <c r="B6" t="n">
-        <v>97333</v>
+        <v>5194</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,21 +1164,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,13 +1188,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529120</v>
+        <v>528875</v>
       </c>
       <c r="R6" t="n">
-        <v>6715242</v>
+        <v>6715153</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,12 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:38</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Fin naturlig bäck med utvidgning.</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,7 +1263,7 @@
         <v>123286624</v>
       </c>
       <c r="B7" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1367,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123303107</v>
+        <v>123286828</v>
       </c>
       <c r="B8" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1401,23 +1411,19 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fisklösen, Falun, Dlr</t>
+          <t>Fisklösen, Fisklösen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529050</v>
+        <v>529029</v>
       </c>
       <c r="R8" t="n">
-        <v>6715233</v>
+        <v>6715126</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,12 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt med bladrosetter på mindre yta.</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,7 +1471,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123283225</v>
+        <v>123283866</v>
       </c>
       <c r="B9" t="n">
-        <v>92247</v>
+        <v>8445</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,46 +1505,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fisklösen, Fisklösen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528881</v>
+        <v>528909</v>
       </c>
       <c r="R9" t="n">
-        <v>6715154</v>
+        <v>6715166</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1573,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,7 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,22 +1589,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123286828</v>
+        <v>123283225</v>
       </c>
       <c r="B10" t="n">
-        <v>98379</v>
+        <v>92264</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1622,41 +1613,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fisklösen, Fisklösen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529029</v>
+        <v>528881</v>
       </c>
       <c r="R10" t="n">
-        <v>6715126</v>
+        <v>6715154</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,10 +1722,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123284412</v>
+        <v>123283973</v>
       </c>
       <c r="B11" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529309</v>
+        <v>529100</v>
       </c>
       <c r="R11" t="n">
-        <v>6715184</v>
+        <v>6715189</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1842,10 +1842,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123283973</v>
+        <v>123284412</v>
       </c>
       <c r="B12" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529100</v>
+        <v>529309</v>
       </c>
       <c r="R12" t="n">
-        <v>6715189</v>
+        <v>6715184</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 5812-2025 artfynd.xlsx
+++ b/artfynd/A 5812-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123284673</v>
+        <v>123283225</v>
       </c>
       <c r="B2" t="n">
-        <v>56697</v>
+        <v>92269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529284</v>
+        <v>528881</v>
       </c>
       <c r="R2" t="n">
-        <v>6715159</v>
+        <v>6715154</v>
       </c>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +784,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123284001</v>
+        <v>123283866</v>
       </c>
       <c r="B3" t="n">
-        <v>97350</v>
+        <v>8447</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529120</v>
+        <v>528909</v>
       </c>
       <c r="R3" t="n">
-        <v>6715242</v>
+        <v>6715166</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:38</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Fin naturlig bäck med utvidgning.</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +896,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123303107</v>
+        <v>123284001</v>
       </c>
       <c r="B4" t="n">
-        <v>98396</v>
+        <v>97367</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,45 +920,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fisklösen, Falun, Dlr</t>
+          <t>Fisklösen, Fisklösen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529050</v>
+        <v>529120</v>
       </c>
       <c r="R4" t="n">
-        <v>6715233</v>
+        <v>6715242</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,12 +993,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt med bladrosetter på mindre yta.</t>
+          <t>Fin naturlig bäck med utvidgning.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,7 +1007,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1034,7 +1028,7 @@
         <v>123286775</v>
       </c>
       <c r="B5" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1148,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123283263</v>
+        <v>123303107</v>
       </c>
       <c r="B6" t="n">
-        <v>5194</v>
+        <v>98502</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1160,41 +1154,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fisklösen, Fisklösen, Dlr</t>
+          <t>Fisklösen, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528875</v>
+        <v>529050</v>
       </c>
       <c r="R6" t="n">
-        <v>6715153</v>
+        <v>6715233</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1223,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1231,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt med bladrosetter på mindre yta.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,6 +1245,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1263,7 +1267,7 @@
         <v>123286624</v>
       </c>
       <c r="B7" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1377,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123286828</v>
+        <v>123284673</v>
       </c>
       <c r="B8" t="n">
-        <v>98396</v>
+        <v>56700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,41 +1393,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fisklösen, Fisklösen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529029</v>
+        <v>529284</v>
       </c>
       <c r="R8" t="n">
-        <v>6715126</v>
+        <v>6715159</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1452,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,22 +1486,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123283866</v>
+        <v>123286828</v>
       </c>
       <c r="B9" t="n">
-        <v>8445</v>
+        <v>98502</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1501,25 +1510,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1529,13 +1538,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528909</v>
+        <v>529029</v>
       </c>
       <c r="R9" t="n">
-        <v>6715166</v>
+        <v>6715126</v>
       </c>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,7 +1573,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1583,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,22 +1598,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123283225</v>
+        <v>123283263</v>
       </c>
       <c r="B10" t="n">
-        <v>92264</v>
+        <v>5196</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,46 +1626,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>105930</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fisklösen, Fisklösen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528881</v>
+        <v>528875</v>
       </c>
       <c r="R10" t="n">
-        <v>6715154</v>
+        <v>6715153</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1725,7 +1725,7 @@
         <v>123283973</v>
       </c>
       <c r="B11" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>123284412</v>
       </c>
       <c r="B12" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 5812-2025 artfynd.xlsx
+++ b/artfynd/A 5812-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123283225</v>
+        <v>123286624</v>
       </c>
       <c r="B2" t="n">
-        <v>92269</v>
+        <v>56700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528881</v>
+        <v>529086</v>
       </c>
       <c r="R2" t="n">
-        <v>6715154</v>
+        <v>6715119</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -911,7 +907,7 @@
         <v>123284001</v>
       </c>
       <c r="B4" t="n">
-        <v>97367</v>
+        <v>97369</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1025,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123286775</v>
+        <v>123286828</v>
       </c>
       <c r="B5" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1065,13 +1061,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529026</v>
+        <v>529029</v>
       </c>
       <c r="R5" t="n">
-        <v>6715120</v>
+        <v>6715126</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,12 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt på cirka 3x0,5 meter</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123303107</v>
+        <v>123286775</v>
       </c>
       <c r="B6" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1176,23 +1167,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fisklösen, Falun, Dlr</t>
+          <t>Fisklösen, Fisklösen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529050</v>
+        <v>529026</v>
       </c>
       <c r="R6" t="n">
-        <v>6715233</v>
+        <v>6715120</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,12 +1218,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt med bladrosetter på mindre yta.</t>
+          <t>Rikligt på cirka 3x0,5 meter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,7 +1232,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1264,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123286624</v>
+        <v>123303107</v>
       </c>
       <c r="B7" t="n">
-        <v>56700</v>
+        <v>98504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,46 +1262,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fisklösen, Fisklösen, Dlr</t>
+          <t>Fisklösen, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529086</v>
+        <v>529050</v>
       </c>
       <c r="R7" t="n">
-        <v>6715119</v>
+        <v>6715233</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1344,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,7 +1339,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt med bladrosetter på mindre yta.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,6 +1353,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1381,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123284673</v>
+        <v>123283225</v>
       </c>
       <c r="B8" t="n">
-        <v>56700</v>
+        <v>92271</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,27 +1388,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1426,13 +1421,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529284</v>
+        <v>528881</v>
       </c>
       <c r="R8" t="n">
-        <v>6715159</v>
+        <v>6715154</v>
       </c>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,7 +1456,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1466,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,22 +1481,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123286828</v>
+        <v>123284673</v>
       </c>
       <c r="B9" t="n">
-        <v>98502</v>
+        <v>56700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,41 +1505,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fisklösen, Fisklösen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529029</v>
+        <v>529284</v>
       </c>
       <c r="R9" t="n">
-        <v>6715126</v>
+        <v>6715159</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,12 +1598,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1722,10 +1722,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123283973</v>
+        <v>123284412</v>
       </c>
       <c r="B11" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529100</v>
+        <v>529309</v>
       </c>
       <c r="R11" t="n">
-        <v>6715189</v>
+        <v>6715184</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1842,10 +1842,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123284412</v>
+        <v>123283973</v>
       </c>
       <c r="B12" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529309</v>
+        <v>529100</v>
       </c>
       <c r="R12" t="n">
-        <v>6715184</v>
+        <v>6715189</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 5812-2025 artfynd.xlsx
+++ b/artfynd/A 5812-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1960,6 +1960,1129 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128050326</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98459</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Fisklösen, Fisklösen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>529008</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6715113</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Knärot i hyggeskant, precis utanför hänsynsytan.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128051043</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98459</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>529033</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6715117</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt med bladrosetter på en större yta, cirka 3,5 meter x 0,5 meter, nästan i mitten på hänsynsytan. Motsvarar ett av tidigare inlagda fynd (2025-03-18). Uppskattat antal - kan ha varit 300-400 plantor.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128050816</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98459</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>529027</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6715116</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Stegat 11 meter till hyggeskant.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128051607</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98459</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>529024</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6715109</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128051421</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98459</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>529039</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6715128</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Här återfanns den enda blomställningen vi såg inom hänsynsytan (överblommad). Stegade 22 meter till närmsta hyggeskant.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128051233</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98459</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>529033</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6715114</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128051193</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98459</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>529032</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6715117</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Moelven markerat denna växtplats med snitsel.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128051293</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98459</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>529032</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6715115</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128049928</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98459</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>529018</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6715119</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Väldigt nära kanten till avverkningen, stegat 3 meter till kantsnitsel.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5812-2025 artfynd.xlsx
+++ b/artfynd/A 5812-2025 artfynd.xlsx
@@ -2203,7 +2203,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128050816</v>
+        <v>128051607</v>
       </c>
       <c r="B15" t="n">
         <v>98459</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2246,18 +2246,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529027</v>
+        <v>529024</v>
       </c>
       <c r="R15" t="n">
-        <v>6715116</v>
+        <v>6715109</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2289,7 +2287,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2299,12 +2297,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:42</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Stegat 11 meter till hyggeskant.</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2313,7 +2306,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2332,7 +2324,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128051607</v>
+        <v>128050816</v>
       </c>
       <c r="B16" t="n">
         <v>98459</v>
@@ -2362,7 +2354,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2375,16 +2367,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529024</v>
+        <v>529027</v>
       </c>
       <c r="R16" t="n">
-        <v>6715109</v>
+        <v>6715116</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2416,7 +2410,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2426,7 +2420,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Stegat 11 meter till hyggeskant.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2435,6 +2434,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5812-2025 artfynd.xlsx
+++ b/artfynd/A 5812-2025 artfynd.xlsx
@@ -1965,7 +1965,7 @@
         <v>128050326</v>
       </c>
       <c r="B13" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>128051043</v>
       </c>
       <c r="B14" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128051607</v>
       </c>
       <c r="B15" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128050816</v>
       </c>
       <c r="B16" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>128051421</v>
       </c>
       <c r="B17" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>128051233</v>
       </c>
       <c r="B18" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2706,10 +2706,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128051193</v>
+        <v>128051293</v>
       </c>
       <c r="B19" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2749,6 +2749,8 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
@@ -2758,7 +2760,7 @@
         <v>529032</v>
       </c>
       <c r="R19" t="n">
-        <v>6715117</v>
+        <v>6715115</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2790,7 +2792,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2800,12 +2802,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Moelven markerat denna växtplats med snitsel.</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2814,6 +2811,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2832,10 +2830,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128051293</v>
+        <v>128051193</v>
       </c>
       <c r="B20" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2862,7 +2860,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2875,8 +2873,6 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
@@ -2886,7 +2882,7 @@
         <v>529032</v>
       </c>
       <c r="R20" t="n">
-        <v>6715115</v>
+        <v>6715117</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2918,7 +2914,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2928,7 +2924,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Moelven markerat denna växtplats med snitsel.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2937,7 +2938,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2959,7 +2959,7 @@
         <v>128049928</v>
       </c>
       <c r="B21" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 5812-2025 artfynd.xlsx
+++ b/artfynd/A 5812-2025 artfynd.xlsx
@@ -1965,7 +1965,7 @@
         <v>128050326</v>
       </c>
       <c r="B13" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>128051043</v>
       </c>
       <c r="B14" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2206,7 +2206,7 @@
         <v>128051607</v>
       </c>
       <c r="B15" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128050816</v>
       </c>
       <c r="B16" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>128051421</v>
       </c>
       <c r="B17" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2585,7 +2585,7 @@
         <v>128051233</v>
       </c>
       <c r="B18" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2709,7 +2709,7 @@
         <v>128051293</v>
       </c>
       <c r="B19" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2833,7 +2833,7 @@
         <v>128051193</v>
       </c>
       <c r="B20" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2959,7 +2959,7 @@
         <v>128049928</v>
       </c>
       <c r="B21" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+          <t>Lisa Olson, Göran Ehn, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 5812-2025 artfynd.xlsx
+++ b/artfynd/A 5812-2025 artfynd.xlsx
@@ -2196,7 +2196,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lisa Olson, Göran Ehn, Cecilia Rastad</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 5812-2025 artfynd.xlsx
+++ b/artfynd/A 5812-2025 artfynd.xlsx
@@ -1965,7 +1965,7 @@
         <v>128050326</v>
       </c>
       <c r="B13" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>128051043</v>
       </c>
       <c r="B14" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128051607</v>
       </c>
       <c r="B15" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128050816</v>
       </c>
       <c r="B16" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>128051421</v>
       </c>
       <c r="B17" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>128051233</v>
       </c>
       <c r="B18" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>128051293</v>
       </c>
       <c r="B19" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>128051193</v>
       </c>
       <c r="B20" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>128049928</v>
       </c>
       <c r="B21" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 5812-2025 artfynd.xlsx
+++ b/artfynd/A 5812-2025 artfynd.xlsx
@@ -1965,7 +1965,7 @@
         <v>128050326</v>
       </c>
       <c r="B13" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>128051043</v>
       </c>
       <c r="B14" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128051607</v>
       </c>
       <c r="B15" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128050816</v>
       </c>
       <c r="B16" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>128051421</v>
       </c>
       <c r="B17" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>128051233</v>
       </c>
       <c r="B18" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>128051293</v>
       </c>
       <c r="B19" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>128051193</v>
       </c>
       <c r="B20" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>128049928</v>
       </c>
       <c r="B21" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 5812-2025 artfynd.xlsx
+++ b/artfynd/A 5812-2025 artfynd.xlsx
@@ -1965,7 +1965,7 @@
         <v>128050326</v>
       </c>
       <c r="B13" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2077,7 +2077,7 @@
         <v>128051043</v>
       </c>
       <c r="B14" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128051607</v>
+        <v>128050816</v>
       </c>
       <c r="B15" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2246,16 +2246,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529024</v>
+        <v>529027</v>
       </c>
       <c r="R15" t="n">
-        <v>6715109</v>
+        <v>6715116</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2287,7 +2289,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2297,7 +2299,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Stegat 11 meter till hyggeskant.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2306,6 +2313,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2317,17 +2325,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128050816</v>
+        <v>128051607</v>
       </c>
       <c r="B16" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,7 +2362,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2367,18 +2375,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529027</v>
+        <v>529024</v>
       </c>
       <c r="R16" t="n">
-        <v>6715116</v>
+        <v>6715109</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2410,7 +2416,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2420,12 +2426,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:42</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Stegat 11 meter till hyggeskant.</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2434,7 +2435,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2456,7 +2456,7 @@
         <v>128051421</v>
       </c>
       <c r="B17" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>128051233</v>
       </c>
       <c r="B18" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2706,10 +2706,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128051293</v>
+        <v>128051193</v>
       </c>
       <c r="B19" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2749,8 +2749,6 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
@@ -2760,7 +2758,7 @@
         <v>529032</v>
       </c>
       <c r="R19" t="n">
-        <v>6715115</v>
+        <v>6715117</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2792,7 +2790,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2802,7 +2800,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Moelven markerat denna växtplats med snitsel.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2811,7 +2814,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2830,10 +2832,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128051193</v>
+        <v>128051293</v>
       </c>
       <c r="B20" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2860,7 +2862,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2873,6 +2875,8 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
@@ -2882,7 +2886,7 @@
         <v>529032</v>
       </c>
       <c r="R20" t="n">
-        <v>6715117</v>
+        <v>6715115</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2914,7 +2918,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2924,12 +2928,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Moelven markerat denna växtplats med snitsel.</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2938,6 +2937,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2959,7 +2959,7 @@
         <v>128049928</v>
       </c>
       <c r="B21" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 5812-2025 artfynd.xlsx
+++ b/artfynd/A 5812-2025 artfynd.xlsx
@@ -1965,7 +1965,7 @@
         <v>128050326</v>
       </c>
       <c r="B13" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2077,7 +2077,7 @@
         <v>128051043</v>
       </c>
       <c r="B14" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128050816</v>
+        <v>128051607</v>
       </c>
       <c r="B15" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2246,18 +2246,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529027</v>
+        <v>529024</v>
       </c>
       <c r="R15" t="n">
-        <v>6715116</v>
+        <v>6715109</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2289,7 +2287,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2299,12 +2297,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:42</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Stegat 11 meter till hyggeskant.</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2313,7 +2306,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2325,17 +2317,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128051607</v>
+        <v>128050816</v>
       </c>
       <c r="B16" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2362,7 +2354,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2375,16 +2367,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529024</v>
+        <v>529027</v>
       </c>
       <c r="R16" t="n">
-        <v>6715109</v>
+        <v>6715116</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2416,7 +2410,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2426,7 +2420,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Stegat 11 meter till hyggeskant.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2435,6 +2434,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2456,7 +2456,7 @@
         <v>128051421</v>
       </c>
       <c r="B17" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>128051233</v>
       </c>
       <c r="B18" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2706,10 +2706,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128051193</v>
+        <v>128051293</v>
       </c>
       <c r="B19" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2749,6 +2749,8 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
@@ -2758,7 +2760,7 @@
         <v>529032</v>
       </c>
       <c r="R19" t="n">
-        <v>6715117</v>
+        <v>6715115</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2790,7 +2792,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2800,12 +2802,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Moelven markerat denna växtplats med snitsel.</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2814,6 +2811,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2832,10 +2830,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128051293</v>
+        <v>128051193</v>
       </c>
       <c r="B20" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2862,7 +2860,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2875,8 +2873,6 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fisklösen, Falun, Fisklösen, Falun, Dlr</t>
@@ -2886,7 +2882,7 @@
         <v>529032</v>
       </c>
       <c r="R20" t="n">
-        <v>6715115</v>
+        <v>6715117</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2918,7 +2914,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2928,7 +2924,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Moelven markerat denna växtplats med snitsel.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2937,7 +2938,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2959,7 +2959,7 @@
         <v>128049928</v>
       </c>
       <c r="B21" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 5812-2025 artfynd.xlsx
+++ b/artfynd/A 5812-2025 artfynd.xlsx
@@ -1965,7 +1965,7 @@
         <v>128050326</v>
       </c>
       <c r="B13" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>128051043</v>
       </c>
       <c r="B14" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>128051607</v>
       </c>
       <c r="B15" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>128050816</v>
       </c>
       <c r="B16" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>128051421</v>
       </c>
       <c r="B17" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>128051233</v>
       </c>
       <c r="B18" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>128051293</v>
       </c>
       <c r="B19" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>128051193</v>
       </c>
       <c r="B20" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>128049928</v>
       </c>
       <c r="B21" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
